--- a/gte/nodes/HPT/turbine_blade_self_frequency.xlsx
+++ b/gte/nodes/HPT/turbine_blade_self_frequency.xlsx
@@ -543,58 +543,58 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>12598.817119889996</v>
+        <v>12595.00587843864</v>
       </c>
       <c r="C3">
-        <v>78961.13790584165</v>
+        <v>78937.251539449513</v>
       </c>
       <c r="D3">
-        <v>221115.71344633194</v>
+        <v>221048.82420072946</v>
       </c>
       <c r="E3">
-        <v>433623.28789523616</v>
+        <v>433492.11343390594</v>
       </c>
       <c r="F3">
-        <v>716516.25398725923</v>
+        <v>716299.50217462622</v>
       </c>
       <c r="G3">
-        <v>1070076.1980847677</v>
+        <v>1069752.4916031638</v>
       </c>
       <c r="H3">
-        <v>8363.700815423028</v>
+        <v>8363.7405012722465</v>
       </c>
       <c r="I3">
-        <v>25091.102446269088</v>
+        <v>25091.221503816741</v>
       </c>
       <c r="J3">
-        <v>41818.50407711514</v>
+        <v>41818.702506361231</v>
       </c>
       <c r="K3">
-        <v>58545.9057079612</v>
+        <v>58546.183508905728</v>
       </c>
       <c r="L3">
-        <v>75273.307338807252</v>
+        <v>75273.664511450217</v>
       </c>
       <c r="M3">
-        <v>92000.708969653322</v>
+        <v>92001.1455139947</v>
       </c>
       <c r="N3">
-        <v>16727.401630846056</v>
+        <v>16727.481002544493</v>
       </c>
       <c r="O3">
-        <v>33454.803261692112</v>
+        <v>33454.962005088986</v>
       </c>
       <c r="P3">
-        <v>50182.204892538175</v>
+        <v>50182.443007633483</v>
       </c>
       <c r="Q3">
-        <v>66909.606523384224</v>
+        <v>66909.924010177972</v>
       </c>
       <c r="R3">
-        <v>83637.00815423028</v>
+        <v>83637.405012722462</v>
       </c>
       <c r="S3">
-        <v>100364.40978507635</v>
+        <v>100364.88601526697</v>
       </c>
     </row>
   </sheetData>
@@ -806,58 +806,58 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>5146.4068300355793</v>
+        <v>5145.4394946295606</v>
       </c>
       <c r="C3">
-        <v>32254.308921149954</v>
+        <v>32248.246296090078</v>
       </c>
       <c r="D3">
-        <v>90322.083976589114</v>
+        <v>90305.106743218043</v>
       </c>
       <c r="E3">
-        <v>177127.88663020235</v>
+        <v>177094.5930951614</v>
       </c>
       <c r="F3">
-        <v>292684.94877428107</v>
+        <v>292629.934757102</v>
       </c>
       <c r="G3">
-        <v>437108.2937451225</v>
+        <v>437026.13344517566</v>
       </c>
       <c r="H3">
-        <v>5506.9078717664943</v>
+        <v>5506.9046857589356</v>
       </c>
       <c r="I3">
-        <v>16520.723615299485</v>
+        <v>16520.714057276808</v>
       </c>
       <c r="J3">
-        <v>27534.53935883247</v>
+        <v>27534.523428794677</v>
       </c>
       <c r="K3">
-        <v>38548.355102365465</v>
+        <v>38548.33280031255</v>
       </c>
       <c r="L3">
-        <v>49562.17084589845</v>
+        <v>49562.142171830426</v>
       </c>
       <c r="M3">
-        <v>60575.986589431443</v>
+        <v>60575.9515433483</v>
       </c>
       <c r="N3">
-        <v>11013.815743532989</v>
+        <v>11013.809371517871</v>
       </c>
       <c r="O3">
-        <v>22027.631487065977</v>
+        <v>22027.618743035742</v>
       </c>
       <c r="P3">
-        <v>33041.447230598969</v>
+        <v>33041.428114553615</v>
       </c>
       <c r="Q3">
-        <v>44055.262974131954</v>
+        <v>44055.237486071484</v>
       </c>
       <c r="R3">
-        <v>55069.078717664939</v>
+        <v>55069.046857589354</v>
       </c>
       <c r="S3">
-        <v>66082.894461197939</v>
+        <v>66082.85622910723</v>
       </c>
     </row>
   </sheetData>
